--- a/questionnaire_templates/026_social_media_fun_questionnaire--questionnaire_templates.xlsx
+++ b/questionnaire_templates/026_social_media_fun_questionnaire--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C103"/>
+  <dimension ref="A1:C102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1245,17 +1245,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>social_media_questionnaire_choices</t>
+          <t>favorite_social_media_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>snapchat</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Snapchat</t>
+          <t>Facebook</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>twitter</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Twitter</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>twitter</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Twitter</t>
+          <t>Instagram</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>instagram</t>
+          <t>tiktok</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>TikTok</t>
         </is>
       </c>
     </row>
@@ -1318,29 +1318,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>tiktok</t>
+          <t>reddit</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Reddit</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>favorite_social_media_choices</t>
+          <t>how_did_you_hear_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>reddit</t>
+          <t>online_search</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Online search</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>online_search</t>
+          <t>social_media_ads</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Online search</t>
+          <t>Social media ads</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>social_media_ads</t>
+          <t>social_media_posts</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Social media ads</t>
+          <t>Social media posts</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>social_media_posts</t>
+          <t>friend_recommendation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Social media posts</t>
+          <t>Friend recommendation</t>
         </is>
       </c>
     </row>
@@ -1403,29 +1403,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>friend_recommendation</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Friend recommendation</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>how_did_you_hear_choices</t>
+          <t>what_do_you_like_to_do_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>listen_to_music</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Listen to music</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>listen_to_music</t>
+          <t>watch_movies/tv_shows</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Listen to music</t>
+          <t>Watch movies/TV shows</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>watch_movies/tv_shows</t>
+          <t>read_books/articles</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Watch movies/TV shows</t>
+          <t>Read books/articles</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>read_books/articles</t>
+          <t>play_sports</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Read books/articles</t>
+          <t>Play sports</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>play_sports</t>
+          <t>travel</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Play sports</t>
+          <t>Travel</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>travel</t>
+          <t>learn_something_new</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Learn something new</t>
         </is>
       </c>
     </row>
@@ -1522,29 +1522,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>learn_something_new</t>
+          <t>create_content</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Learn something new</t>
+          <t>Create content</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>what_do_you_like_to_do_choices</t>
+          <t>social_media_habits_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>create_content</t>
+          <t>check_social_media_daily</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Create content</t>
+          <t>Check social media daily</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>check_social_media_daily</t>
+          <t>check_social_media_hourly</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Check social media daily</t>
+          <t>Check social media hourly</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>check_social_media_hourly</t>
+          <t>check_social_media_every_2-3_days</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Check social media hourly</t>
+          <t>Check social media every 2-3 days</t>
         </is>
       </c>
     </row>
@@ -1590,29 +1590,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>check_social_media_every_2-3_days</t>
+          <t>never_check_social_media</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Check social media every 2-3 days</t>
+          <t>Never check social media</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>social_media_habits_choices</t>
+          <t>favorite_content_type_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>never_check_social_media</t>
+          <t>article</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Never check social media</t>
+          <t>Article</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>video</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Video</t>
         </is>
       </c>
     </row>
@@ -1641,29 +1641,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>post</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>Post</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>favorite_content_type_choices</t>
+          <t>how_much_time_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>less_than_1_hour</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Less than 1 hour</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>less_than_1_hour</t>
+          <t>1-2_hours</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Less than 1 hour</t>
+          <t>1-2 hours</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1-2_hours</t>
+          <t>2-4_hours</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1-2 hours</t>
+          <t>2-4 hours</t>
         </is>
       </c>
     </row>
@@ -1709,29 +1709,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2-4_hours</t>
+          <t>more_than_4_hours</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2-4 hours</t>
+          <t>More than 4 hours</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>how_much_time_choices</t>
+          <t>why_do_you_use_social_media_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>more_than_4_hours</t>
+          <t>to_connect_with_people</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>More than 4 hours</t>
+          <t>To connect with people</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>to_connect_with_people</t>
+          <t>to_stay_updated</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>To connect with people</t>
+          <t>To stay updated</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>to_stay_updated</t>
+          <t>to_escape_reality</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>To stay updated</t>
+          <t>To escape reality</t>
         </is>
       </c>
     </row>
@@ -1777,29 +1777,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>to_escape_reality</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>To escape reality</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>why_do_you_use_social_media_choices</t>
+          <t>what_do_you_share_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>photos</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Photos</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>photos</t>
+          <t>videos</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Photos</t>
+          <t>Videos</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>videos</t>
+          <t>posts</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Videos</t>
+          <t>Posts</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>posts</t>
+          <t>stories</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Posts</t>
+          <t>Stories</t>
         </is>
       </c>
     </row>
@@ -1862,29 +1862,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>stories</t>
+          <t>reels</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Stories</t>
+          <t>Reels</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>what_do_you_share_choices</t>
+          <t>social_media_frequency_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>reels</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Reels</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1913,29 +1913,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>social_media_frequency_choices</t>
+          <t>what_do_you_like_to_share_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>fun_posts</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Fun posts</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>fun_posts</t>
+          <t>educational_content</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Fun posts</t>
+          <t>Educational content</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>educational_content</t>
+          <t>product_reviews</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Educational content</t>
+          <t>Product reviews</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>product_reviews</t>
+          <t>event_invitations</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Product reviews</t>
+          <t>Event invitations</t>
         </is>
       </c>
     </row>
@@ -1998,29 +1998,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>event_invitations</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Event invitations</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>what_do_you_like_to_share_choices</t>
+          <t>social_media_goals_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>increase_followers</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Increase followers</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>increase_followers</t>
+          <t>increase_engagement</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Increase followers</t>
+          <t>Increase engagement</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>increase_engagement</t>
+          <t>build_a_community</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Increase engagement</t>
+          <t>Build a community</t>
         </is>
       </c>
     </row>
@@ -2066,29 +2066,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>build_a_community</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Build a community</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>social_media_goals_choices</t>
+          <t>social_media_influences_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>family</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Family</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>family</t>
+          <t>friends</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Family</t>
+          <t>Friends</t>
         </is>
       </c>
     </row>
@@ -2117,12 +2117,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>friends</t>
+          <t>celebrities</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Friends</t>
+          <t>Celebrities</t>
         </is>
       </c>
     </row>
@@ -2134,29 +2134,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>celebrities</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Celebrities</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>social_media_influences_choices</t>
+          <t>social_media_platforms_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Facebook</t>
         </is>
       </c>
     </row>
@@ -2168,12 +2168,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Instagram</t>
         </is>
       </c>
     </row>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>instagram</t>
+          <t>twitter</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Twitter</t>
         </is>
       </c>
     </row>
@@ -2202,12 +2202,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>twitter</t>
+          <t>tiktok</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Twitter</t>
+          <t>TikTok</t>
         </is>
       </c>
     </row>
@@ -2219,12 +2219,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>tiktok</t>
+          <t>snapchat</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Snapchat</t>
         </is>
       </c>
     </row>
@@ -2236,12 +2236,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>snapchat</t>
+          <t>youtube</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Snapchat</t>
+          <t>YouTube</t>
         </is>
       </c>
     </row>
@@ -2253,29 +2253,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>youtube</t>
+          <t>reddit</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Reddit</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>social_media_platforms_choices</t>
+          <t>social_media_content_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>reddit</t>
+          <t>photos</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Photos</t>
         </is>
       </c>
     </row>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>photos</t>
+          <t>videos</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Photos</t>
+          <t>Videos</t>
         </is>
       </c>
     </row>
@@ -2304,12 +2304,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>videos</t>
+          <t>posts</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Videos</t>
+          <t>Posts</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>posts</t>
+          <t>stories</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Posts</t>
+          <t>Stories</t>
         </is>
       </c>
     </row>
@@ -2338,12 +2338,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>stories</t>
+          <t>reels</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Stories</t>
+          <t>Reels</t>
         </is>
       </c>
     </row>
@@ -2355,29 +2355,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>reels</t>
+          <t>live_streams</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Reels</t>
+          <t>Live streams</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>social_media_content_choices</t>
+          <t>favorite_social_media_platform_choices</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>live_streams</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Live streams</t>
+          <t>Facebook</t>
         </is>
       </c>
     </row>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Instagram</t>
         </is>
       </c>
     </row>
@@ -2406,12 +2406,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>instagram</t>
+          <t>twitter</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Twitter</t>
         </is>
       </c>
     </row>
@@ -2423,12 +2423,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>twitter</t>
+          <t>tiktok</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Twitter</t>
+          <t>TikTok</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>tiktok</t>
+          <t>snapchat</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Snapchat</t>
         </is>
       </c>
     </row>
@@ -2457,12 +2457,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>snapchat</t>
+          <t>youtube</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Snapchat</t>
+          <t>YouTube</t>
         </is>
       </c>
     </row>
@@ -2474,29 +2474,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>youtube</t>
+          <t>reddit</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Reddit</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>favorite_social_media_platform_choices</t>
+          <t>social_media_trends_choices</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>reddit</t>
+          <t>sports</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Sports</t>
         </is>
       </c>
     </row>
@@ -2508,12 +2508,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>entertainment</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Entertainment</t>
         </is>
       </c>
     </row>
@@ -2525,12 +2525,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>entertainment</t>
+          <t>politics</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Entertainment</t>
+          <t>Politics</t>
         </is>
       </c>
     </row>
@@ -2542,12 +2542,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>politics</t>
+          <t>news</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Politics</t>
+          <t>News</t>
         </is>
       </c>
     </row>
@@ -2559,29 +2559,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>news</t>
+          <t>fashion</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>Fashion</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>social_media_trends_choices</t>
+          <t>content_type_choices</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>fashion</t>
+          <t>articles</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Fashion</t>
+          <t>Articles</t>
         </is>
       </c>
     </row>
@@ -2593,12 +2593,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>articles</t>
+          <t>videos</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Articles</t>
+          <t>Videos</t>
         </is>
       </c>
     </row>
@@ -2610,12 +2610,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>videos</t>
+          <t>live_streams</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Videos</t>
+          <t>Live streams</t>
         </is>
       </c>
     </row>
@@ -2627,12 +2627,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>live_streams</t>
+          <t>posts</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Live streams</t>
+          <t>Posts</t>
         </is>
       </c>
     </row>
@@ -2644,12 +2644,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>posts</t>
+          <t>stories</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Posts</t>
+          <t>Stories</t>
         </is>
       </c>
     </row>
@@ -2661,29 +2661,29 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>stories</t>
+          <t>reels</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Stories</t>
+          <t>Reels</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>content_type_choices</t>
+          <t>content_frequency_choices</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>reels</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Reels</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -2695,12 +2695,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -2712,29 +2712,29 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>content_frequency_choices</t>
+          <t>favorite_content_platform_choices</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>youtube</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>YouTube</t>
         </is>
       </c>
     </row>
@@ -2746,12 +2746,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>youtube</t>
+          <t>tiktok</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>TikTok</t>
         </is>
       </c>
     </row>
@@ -2763,12 +2763,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>tiktok</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Instagram</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>instagram</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Facebook</t>
         </is>
       </c>
     </row>
@@ -2797,12 +2797,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>snapchat</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Snapchat</t>
         </is>
       </c>
     </row>
@@ -2814,12 +2814,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>snapchat</t>
+          <t>twitter</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Snapchat</t>
+          <t>Twitter</t>
         </is>
       </c>
     </row>
@@ -2831,27 +2831,10 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>twitter</t>
+          <t>reddit</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
-        <is>
-          <t>Twitter</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>favorite_content_platform_choices</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>reddit</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
         <is>
           <t>Reddit</t>
         </is>
